--- a/data/00988A_20260826.xlsx
+++ b/data/00988A_20260826.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="208">
-  <si>
-    <t xml:space="preserve">資料日期：115/08/24</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="197">
+  <si>
+    <t xml:space="preserve">資料日期：115/08/25</t>
   </si>
   <si>
     <t xml:space="preserve">基金資產</t>
@@ -23,19 +23,19 @@
     <t xml:space="preserve">淨資產</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 53,413,655,044</t>
+    <t xml:space="preserve">NTD 54,440,410,074</t>
   </si>
   <si>
     <t xml:space="preserve">流通在外單位數</t>
   </si>
   <si>
-    <t xml:space="preserve">3,351,937,000</t>
+    <t xml:space="preserve">3,353,437,000</t>
   </si>
   <si>
     <t xml:space="preserve">每單位淨值</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 15.94</t>
+    <t xml:space="preserve">NTD 16.23</t>
   </si>
   <si>
     <t xml:space="preserve">項目</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">股票</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 51,544,605,588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.50%</t>
+    <t xml:space="preserve">NTD 51,709,839,506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.98%</t>
   </si>
   <si>
     <t xml:space="preserve">現金</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 2,417,602,598</t>
+    <t xml:space="preserve">NTD 1,980,219,969</t>
   </si>
   <si>
     <t xml:space="preserve">期貨保證金</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">應收付證券款</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 274,587,171</t>
+    <t xml:space="preserve">NTD 839,381,926</t>
   </si>
   <si>
     <t xml:space="preserve">股票代號</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">117,000</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80%</t>
+    <t xml:space="preserve">6.07%</t>
   </si>
   <si>
     <t xml:space="preserve">3037</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">445,000</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52%</t>
+    <t xml:space="preserve">4.57%</t>
   </si>
   <si>
     <t xml:space="preserve">009150 KS</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">70,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95%</t>
+    <t xml:space="preserve">4.07%</t>
   </si>
   <si>
     <t xml:space="preserve">MU US</t>
@@ -152,7 +152,19 @@
     <t xml:space="preserve">MICRON TECHNOLOGY INC</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81%</t>
+    <t xml:space="preserve">3.83%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMD US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADVANCED MICRO DEVICES.amd us(超微半導體公司)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65%</t>
   </si>
   <si>
     <t xml:space="preserve">6981 JP</t>
@@ -164,19 +176,7 @@
     <t xml:space="preserve">1,350,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMD US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADVANCED MICRO DEVICES.amd us(超微半導體公司)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55%</t>
+    <t xml:space="preserve">3.54%</t>
   </si>
   <si>
     <t xml:space="preserve">285A JP</t>
@@ -188,7 +188,19 @@
     <t xml:space="preserve">180,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44%</t>
+    <t xml:space="preserve">3.39%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOOM ENERGY CORP- A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18%</t>
   </si>
   <si>
     <t xml:space="preserve">PANW US</t>
@@ -200,7 +212,7 @@
     <t xml:space="preserve">150,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14%</t>
+    <t xml:space="preserve">2.99%</t>
   </si>
   <si>
     <t xml:space="preserve">CRDO US</t>
@@ -212,7 +224,25 @@
     <t xml:space="preserve">225,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99%</t>
+    <t xml:space="preserve">STX US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEAGATE TECHNOLOGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRVL US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARVELL TECHNOLOGY INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205,000</t>
   </si>
   <si>
     <t xml:space="preserve">2330</t>
@@ -224,31 +254,7 @@
     <t xml:space="preserve">650,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STX US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEAGATE TECHNOLOGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRVL US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARVELL TECHNOLOGY INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81%</t>
+    <t xml:space="preserve">2.87%</t>
   </si>
   <si>
     <t xml:space="preserve">TSEM US</t>
@@ -260,19 +266,19 @@
     <t xml:space="preserve">216,825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOOM ENERGY CORP- A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56%</t>
+    <t xml:space="preserve">2.70%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCL US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLE INTERNET GROUP INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">480,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59%</t>
   </si>
   <si>
     <t xml:space="preserve">6223</t>
@@ -284,7 +290,19 @@
     <t xml:space="preserve">242,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52%</t>
+    <t xml:space="preserve">2.49%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPCX US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPACE EXPLORATION TECHN-CL A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42%</t>
   </si>
   <si>
     <t xml:space="preserve">SNOW US</t>
@@ -293,19 +311,7 @@
     <t xml:space="preserve">SNOWFLAKE INC-CLASS A(Snowflake公司)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPCX US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPACE EXPLORATION TECHN-CL A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42%</t>
+    <t xml:space="preserve">2.41%</t>
   </si>
   <si>
     <t xml:space="preserve">2308</t>
@@ -317,7 +323,109 @@
     <t xml:space="preserve">720,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34%</t>
+    <t xml:space="preserve">2.26%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6871 JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICRONICS JAPAN CO LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">370,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLTR US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALANTIR TECHNOLOGIES INC-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNDK US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDISK CORP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300408 CH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAOZHOU THREE-CIRCLE GROU-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,749,879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COHR US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COHERENT INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFX GY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFINEON TECHNOLOGIES AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">425,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">國巨*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,550,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇鋐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPWR US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONOLITHIC POWER SYSTEMS INC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38%</t>
   </si>
   <si>
     <t xml:space="preserve">2454</t>
@@ -326,121 +434,10 @@
     <t xml:space="preserve">聯發科</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRCL US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLE INTERNET GROUP INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLTR US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALANTIR TECHNOLOGIES INC-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6871 JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICRONICS JAPAN CO LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">370,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNDK US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANDISK CORP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300408 CH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAOZHOU THREE-CIRCLE GROU-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,749,879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFX GY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFINEON TECHNOLOGIES AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">425,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">國巨*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,550,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COHR US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COHERENT INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇鋐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPWR US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONOLITHIC POWER SYSTEMS INC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38%</t>
+    <t xml:space="preserve">200,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37%</t>
   </si>
   <si>
     <t xml:space="preserve">6997 JP</t>
@@ -452,7 +449,7 @@
     <t xml:space="preserve">1,275,100</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29%</t>
+    <t xml:space="preserve">1.26%</t>
   </si>
   <si>
     <t xml:space="preserve">TER US</t>
@@ -464,19 +461,7 @@
     <t xml:space="preserve">55,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日月光投控</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,000,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11%</t>
+    <t xml:space="preserve">1.18%</t>
   </si>
   <si>
     <t xml:space="preserve">000660 KS</t>
@@ -488,19 +473,7 @@
     <t xml:space="preserve">15,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDC US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WESTERN DIGITAL CORP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04%</t>
+    <t xml:space="preserve">1.09%</t>
   </si>
   <si>
     <t xml:space="preserve">301377 CH</t>
@@ -512,7 +485,7 @@
     <t xml:space="preserve">291,988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02%</t>
+    <t xml:space="preserve">1.00%</t>
   </si>
   <si>
     <t xml:space="preserve">FORM US</t>
@@ -524,7 +497,7 @@
     <t xml:space="preserve">150,454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97%</t>
+    <t xml:space="preserve">0.95%</t>
   </si>
   <si>
     <t xml:space="preserve">3308 HK</t>
@@ -536,7 +509,19 @@
     <t xml:space="preserve">110,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85%</t>
+    <t xml:space="preserve">0.83%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">華星光</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81%</t>
   </si>
   <si>
     <t xml:space="preserve">AEM US</t>
@@ -545,7 +530,7 @@
     <t xml:space="preserve">AGNICO EAGLE MINES LTD</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78%</t>
+    <t xml:space="preserve">0.79%</t>
   </si>
   <si>
     <t xml:space="preserve">NET US</t>
@@ -557,7 +542,16 @@
     <t xml:space="preserve">45,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75%</t>
+    <t xml:space="preserve">0.73%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5801 JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FURUKAWA ELECTRIC CO LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500,000</t>
   </si>
   <si>
     <t xml:space="preserve">TWLO US</t>
@@ -566,19 +560,7 @@
     <t xml:space="preserve">TWILIO INC - A</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5801 JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FURUKAWA ELECTRIC CO LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68%</t>
+    <t xml:space="preserve">0.72%</t>
   </si>
   <si>
     <t xml:space="preserve">AIXA GY</t>
@@ -587,9 +569,6 @@
     <t xml:space="preserve">AIXTRON SE</t>
   </si>
   <si>
-    <t xml:space="preserve">200,000</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.51%</t>
   </si>
   <si>
@@ -602,19 +581,7 @@
     <t xml:space="preserve">950,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">華星光</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46%</t>
+    <t xml:space="preserve">0.45%</t>
   </si>
   <si>
     <t xml:space="preserve">AEHR US</t>
@@ -623,7 +590,7 @@
     <t xml:space="preserve">AEHR TEST SYSTEMS</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40%</t>
+    <t xml:space="preserve">0.39%</t>
   </si>
   <si>
     <t xml:space="preserve">095340 KS</t>
@@ -635,7 +602,7 @@
     <t xml:space="preserve">50,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33%</t>
+    <t xml:space="preserve">0.35%</t>
   </si>
 </sst>
 </file>
@@ -714,7 +681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
@@ -796,30 +763,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1376,10 +1319,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.55" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.35" bestFit="1" customWidth="1"/>
@@ -1675,511 +1618,483 @@
         <v>69</v>
       </c>
       <c r="D31" s="74" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="76" t="s">
+      <c r="C32" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="77" t="s">
+      <c r="D32" s="78" t="s">
         <v>73</v>
-      </c>
-      <c r="D32" s="78" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="80" t="s">
+      <c r="C33" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="81" t="s">
-        <v>77</v>
-      </c>
       <c r="D33" s="82" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="83" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="84" t="s">
+      <c r="D34" s="86" t="s">
         <v>80</v>
-      </c>
-      <c r="C34" s="85" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="86" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="88" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="88" t="s">
+      <c r="D35" s="90" t="s">
         <v>84</v>
-      </c>
-      <c r="C35" s="89" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="90" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="92" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="B36" s="92" t="s">
+      <c r="D36" s="94" t="s">
         <v>88</v>
-      </c>
-      <c r="C36" s="93" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" s="94" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="95" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="96" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="D37" s="98" t="s">
         <v>92</v>
-      </c>
-      <c r="C37" s="97" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="98" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="99" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="B38" s="100" t="s">
+      <c r="C38" s="101" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="101" t="s">
+      <c r="D38" s="102" t="s">
         <v>96</v>
-      </c>
-      <c r="D38" s="102" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="104" t="s">
+      <c r="C39" s="105" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" s="106" t="s">
         <v>99</v>
-      </c>
-      <c r="C39" s="105" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" s="106" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="107" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="108" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="109" t="s">
         <v>102</v>
       </c>
-      <c r="B40" s="108" t="s">
+      <c r="D40" s="110" t="s">
         <v>103</v>
-      </c>
-      <c r="C40" s="109" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="110" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="111" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" s="112" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="112" t="s">
+      <c r="C41" s="113" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="113" t="s">
+      <c r="D41" s="114" t="s">
         <v>107</v>
-      </c>
-      <c r="D41" s="114" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="115" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="116" t="s">
         <v>109</v>
-      </c>
-      <c r="B42" s="116" t="s">
-        <v>110</v>
       </c>
       <c r="C42" s="117" t="s">
         <v>57</v>
       </c>
       <c r="D42" s="118" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="119" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="120" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="120" t="s">
+      <c r="C43" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="C43" s="121" t="s">
-        <v>114</v>
-      </c>
       <c r="D43" s="122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="123" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="124" t="s">
         <v>115</v>
       </c>
-      <c r="B44" s="124" t="s">
+      <c r="C44" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="125" t="s">
+      <c r="D44" s="126" t="s">
         <v>117</v>
-      </c>
-      <c r="D44" s="126" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="127" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="B45" s="128" t="s">
+      <c r="C45" s="129" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="129" t="s">
+      <c r="D45" s="130" t="s">
         <v>121</v>
-      </c>
-      <c r="D45" s="130" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="131" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="132" t="s">
+      <c r="C46" s="133" t="s">
         <v>124</v>
       </c>
-      <c r="C46" s="133" t="s">
+      <c r="D46" s="134" t="s">
         <v>125</v>
-      </c>
-      <c r="D46" s="134" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="135" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="136" t="s">
         <v>127</v>
       </c>
-      <c r="B47" s="136" t="s">
+      <c r="C47" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="C47" s="137" t="s">
+      <c r="D47" s="138" t="s">
         <v>129</v>
-      </c>
-      <c r="D47" s="138" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="139" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="140" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="140" t="s">
+      <c r="C48" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="141" t="s">
+      <c r="D48" s="142" t="s">
         <v>133</v>
-      </c>
-      <c r="D48" s="142" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="143" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" s="144" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="144" t="s">
+      <c r="C49" s="145" t="s">
         <v>136</v>
       </c>
-      <c r="C49" s="145" t="s">
+      <c r="D49" s="146" t="s">
         <v>137</v>
-      </c>
-      <c r="D49" s="146" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="147" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" s="148" t="s">
         <v>139</v>
       </c>
-      <c r="B50" s="148" t="s">
+      <c r="C50" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="C50" s="149" t="s">
+      <c r="D50" s="150" t="s">
         <v>141</v>
-      </c>
-      <c r="D50" s="150" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="151" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="152" t="s">
         <v>143</v>
       </c>
-      <c r="B51" s="152" t="s">
+      <c r="C51" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="C51" s="153" t="s">
+      <c r="D51" s="154" t="s">
         <v>145</v>
-      </c>
-      <c r="D51" s="154" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="155" t="s">
+        <v>146</v>
+      </c>
+      <c r="B52" s="156" t="s">
         <v>147</v>
       </c>
-      <c r="B52" s="156" t="s">
+      <c r="C52" s="157" t="s">
         <v>148</v>
       </c>
-      <c r="C52" s="157" t="s">
+      <c r="D52" s="158" t="s">
         <v>149</v>
-      </c>
-      <c r="D52" s="158" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="159" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53" s="160" t="s">
         <v>151</v>
       </c>
-      <c r="B53" s="160" t="s">
+      <c r="C53" s="161" t="s">
         <v>152</v>
       </c>
-      <c r="C53" s="161" t="s">
+      <c r="D53" s="162" t="s">
         <v>153</v>
-      </c>
-      <c r="D53" s="162" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="163" t="s">
+        <v>154</v>
+      </c>
+      <c r="B54" s="164" t="s">
         <v>155</v>
       </c>
-      <c r="B54" s="164" t="s">
+      <c r="C54" s="165" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="165" t="s">
+      <c r="D54" s="166" t="s">
         <v>157</v>
-      </c>
-      <c r="D54" s="166" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="167" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="168" t="s">
         <v>159</v>
       </c>
-      <c r="B55" s="168" t="s">
+      <c r="C55" s="169" t="s">
         <v>160</v>
       </c>
-      <c r="C55" s="169" t="s">
+      <c r="D55" s="170" t="s">
         <v>161</v>
-      </c>
-      <c r="D55" s="170" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="171" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="172" t="s">
         <v>163</v>
       </c>
-      <c r="B56" s="172" t="s">
+      <c r="C56" s="173" t="s">
         <v>164</v>
       </c>
-      <c r="C56" s="173" t="s">
+      <c r="D56" s="174" t="s">
         <v>165</v>
-      </c>
-      <c r="D56" s="174" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="175" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" s="176" t="s">
         <v>167</v>
       </c>
-      <c r="B57" s="176" t="s">
+      <c r="C57" s="177" t="s">
         <v>168</v>
       </c>
-      <c r="C57" s="177" t="s">
+      <c r="D57" s="178" t="s">
         <v>169</v>
-      </c>
-      <c r="D57" s="178" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="179" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" s="180" t="s">
         <v>171</v>
       </c>
-      <c r="B58" s="180" t="s">
+      <c r="C58" s="181" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="182" t="s">
         <v>172</v>
-      </c>
-      <c r="C58" s="181" t="s">
-        <v>173</v>
-      </c>
-      <c r="D58" s="182" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="183" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" s="184" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="185" t="s">
         <v>175</v>
       </c>
-      <c r="B59" s="184" t="s">
+      <c r="D59" s="186" t="s">
         <v>176</v>
-      </c>
-      <c r="C59" s="185" t="s">
-        <v>73</v>
-      </c>
-      <c r="D59" s="186" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="187" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="188" t="s">
         <v>178</v>
       </c>
-      <c r="B60" s="188" t="s">
+      <c r="C60" s="189" t="s">
         <v>179</v>
       </c>
-      <c r="C60" s="189" t="s">
-        <v>180</v>
-      </c>
       <c r="D60" s="190" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="191" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" s="192" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" s="194" t="s">
         <v>182</v>
-      </c>
-      <c r="B61" s="192" t="s">
-        <v>183</v>
-      </c>
-      <c r="C61" s="193" t="s">
-        <v>149</v>
-      </c>
-      <c r="D61" s="194" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="195" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" s="196" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="197" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" s="198" t="s">
         <v>185</v>
-      </c>
-      <c r="B62" s="196" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="197" t="s">
-        <v>187</v>
-      </c>
-      <c r="D62" s="198" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="199" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" s="200" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="201" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" s="202" t="s">
         <v>189</v>
-      </c>
-      <c r="B63" s="200" t="s">
-        <v>190</v>
-      </c>
-      <c r="C63" s="201" t="s">
-        <v>191</v>
-      </c>
-      <c r="D63" s="202" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="203" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B64" s="204" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C64" s="205" t="s">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="D64" s="206" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="207" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B65" s="208" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C65" s="209" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="211" t="s">
-        <v>201</v>
-      </c>
-      <c r="B66" s="212" t="s">
-        <v>202</v>
-      </c>
-      <c r="C66" s="213" t="s">
-        <v>42</v>
-      </c>
-      <c r="D66" s="214" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="215" t="s">
-        <v>204</v>
-      </c>
-      <c r="B67" s="216" t="s">
-        <v>205</v>
-      </c>
-      <c r="C67" s="217" t="s">
-        <v>206</v>
-      </c>
-      <c r="D67" s="218" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
